--- a/docs/DocFacil-Kit-Vendedor-2026.xlsx
+++ b/docs/DocFacil-Kit-Vendedor-2026.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="296">
   <si>
     <t>DocFácil — Kit de Vendedor 2026</t>
   </si>
@@ -119,7 +119,7 @@
     <t>—</t>
   </si>
   <si>
-    <t>Doctores curiosos. Gancho para conversión.</t>
+    <t>Doctores curiosos. Sin comisión. Gancho para conversión.</t>
   </si>
   <si>
     <t>BÁSICO</t>
@@ -131,7 +131,7 @@
     <t>$149 (50% off)</t>
   </si>
   <si>
-    <t>Doctores individuales que buscan eficiencia básica.</t>
+    <t>Doctores individuales. Comisión: $448.50 por venta.</t>
   </si>
   <si>
     <t>PRO ⭐</t>
@@ -146,7 +146,7 @@
     <t>Ilimitados</t>
   </si>
   <si>
-    <t>EL QUE MÁS VENDE. Incluye TODA la IA.</t>
+    <t>EL QUE MÁS VENDE. TODA la IA. Comisión: $898.50 por venta.</t>
   </si>
   <si>
     <t>CLÍNICA</t>
@@ -158,10 +158,10 @@
     <t>$599 (50% off)</t>
   </si>
   <si>
-    <t>Clínicas con 4+ doctores. Multi-sucursal.</t>
-  </si>
-  <si>
-    <t>⚠️ IMPORTANTE: Las comisiones solo se pagan por planes PRO y CLÍNICA (NO Free ni Básico)</t>
+    <t>Clínicas grandes. Comisión: $1,798.50 por venta.</t>
+  </si>
+  <si>
+    <t>✅ TODOS los planes de pago (Básico, Pro y Clínica) pagan comisión. Solo el plan Free NO.</t>
   </si>
   <si>
     <t>✨ FEATURES INCLUIDAS POR PLAN</t>
@@ -686,6 +686,12 @@
     <t>Básico</t>
   </si>
   <si>
+    <t>$448.50</t>
+  </si>
+  <si>
+    <t>$224.25 + $224.25</t>
+  </si>
+  <si>
     <t>Pro ⭐</t>
   </si>
   <si>
@@ -722,13 +728,13 @@
     <t>Starter</t>
   </si>
   <si>
-    <t>3 Pro</t>
-  </si>
-  <si>
-    <t>3 x $898</t>
-  </si>
-  <si>
-    <t>$2,695</t>
+    <t>3 Básico + 2 Pro</t>
+  </si>
+  <si>
+    <t>3x$448.50 + 2x$898.50</t>
+  </si>
+  <si>
+    <t>$3,142.50</t>
   </si>
   <si>
     <t>Medium</t>
@@ -737,10 +743,10 @@
     <t>5 Pro + 1 Clínica</t>
   </si>
   <si>
-    <t>5x$898 + 1x$1,798</t>
-  </si>
-  <si>
-    <t>$6,290</t>
+    <t>5x$898.50 + 1x$1,798.50</t>
+  </si>
+  <si>
+    <t>$6,291</t>
   </si>
   <si>
     <t>Top</t>
@@ -749,10 +755,22 @@
     <t>10 Pro + 2 Clínica</t>
   </si>
   <si>
-    <t>10x$898 + 2x$1,798</t>
-  </si>
-  <si>
-    <t>$12,580</t>
+    <t>10x$898.50 + 2x$1,798.50</t>
+  </si>
+  <si>
+    <t>$12,582</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>5 Básico + 10 Pro + 3 Clínica</t>
+  </si>
+  <si>
+    <t>Mix completo</t>
+  </si>
+  <si>
+    <t>$16,618.50</t>
   </si>
   <si>
     <t>🔗 LINKS IMPORTANTES</t>
@@ -983,7 +1001,7 @@
       <strike val="0"/>
       <u val="none"/>
       <sz val="12"/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FF065F46"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1113,7 +1131,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
+        <fgColor rgb="FFD1FAE5"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1694,161 +1712,161 @@
   <sheetData>
     <row r="1" spans="1:3" customHeight="1" ht="40">
       <c r="A1" s="5" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:3" customHeight="1" ht="25">
       <c r="A3" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:3" customHeight="1" ht="25">
       <c r="A4" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:3" customHeight="1" ht="25">
       <c r="A5" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:3" customHeight="1" ht="25">
       <c r="A6" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:3" customHeight="1" ht="25">
       <c r="A7" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:3" customHeight="1" ht="25">
       <c r="A8" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:3" customHeight="1" ht="25">
       <c r="A9" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:3" customHeight="1" ht="25">
       <c r="A10" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:3" customHeight="1" ht="25">
       <c r="A11" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:3" customHeight="1" ht="25">
       <c r="A12" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:3" customHeight="1" ht="25">
       <c r="A13" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:3" customHeight="1" ht="25">
       <c r="A14" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:3" customHeight="1" ht="25">
       <c r="A15" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:3" customHeight="1" ht="25">
       <c r="A16" s="39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -3261,7 +3279,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="true" style="0"/>
@@ -3321,99 +3339,113 @@
         <v>33</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>29</v>
+        <v>220</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="19" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="35" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -3443,71 +3475,71 @@
   <sheetData>
     <row r="1" spans="1:2" customHeight="1" ht="40">
       <c r="A1" s="5" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:2" customHeight="1" ht="25">
       <c r="A3" s="37" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:2" customHeight="1" ht="25">
       <c r="A4" s="37" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:2" customHeight="1" ht="25">
       <c r="A5" s="37" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:2" customHeight="1" ht="25">
       <c r="A6" s="37" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:2" customHeight="1" ht="25">
       <c r="A7" s="37" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:2" customHeight="1" ht="25">
       <c r="A8" s="37" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:2" customHeight="1" ht="25">
       <c r="A9" s="37" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:2" customHeight="1" ht="25">
       <c r="A10" s="37" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/docs/DocFacil-Kit-Vendedor-2026.xlsx
+++ b/docs/DocFacil-Kit-Vendedor-2026.xlsx
@@ -4,19 +4,18 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="9" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="8" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="1" r:id="rId4"/>
     <sheet name="Planes y Precios" sheetId="2" r:id="rId5"/>
     <sheet name="Features por Plan" sheetId="3" r:id="rId6"/>
-    <sheet name="Features IA" sheetId="4" r:id="rId7"/>
-    <sheet name="vs Competencia" sheetId="5" r:id="rId8"/>
-    <sheet name="Script de Venta" sheetId="6" r:id="rId9"/>
-    <sheet name="Calculadora ROI" sheetId="7" r:id="rId10"/>
-    <sheet name="Comisiones" sheetId="8" r:id="rId11"/>
-    <sheet name="Links y Recursos" sheetId="9" r:id="rId12"/>
-    <sheet name="Checklist" sheetId="10" r:id="rId13"/>
+    <sheet name="vs Competencia" sheetId="4" r:id="rId7"/>
+    <sheet name="Script de Venta" sheetId="5" r:id="rId8"/>
+    <sheet name="Calculadora ROI" sheetId="6" r:id="rId9"/>
+    <sheet name="Comisiones" sheetId="7" r:id="rId10"/>
+    <sheet name="Links y Recursos" sheetId="8" r:id="rId11"/>
+    <sheet name="Checklist" sheetId="9" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -24,12 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="236">
   <si>
     <t>DocFácil — Kit de Vendedor 2026</t>
   </si>
   <si>
-    <t>El único software médico con IA de verdad en México</t>
+    <t>Software para consultorios médicos y dentales en México</t>
   </si>
   <si>
     <t>ÍNDICE DEL KIT</t>
@@ -47,43 +46,37 @@
     <t>Comparativa detallada de qué incluye cada plan</t>
   </si>
   <si>
-    <t>3. Features con IA</t>
-  </si>
-  <si>
-    <t>12 features con Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>4. Competencia</t>
+    <t>3. Competencia</t>
   </si>
   <si>
     <t>Comparativa vs SimplyBook, Abysmed, Doctoralia, iPraxis</t>
   </si>
   <si>
-    <t>5. Script de Venta</t>
+    <t>4. Script de Venta</t>
   </si>
   <si>
     <t>Argumentos clave y respuestas a objeciones</t>
   </si>
   <si>
-    <t>6. Calculadora ROI</t>
+    <t>5. Calculadora ROI</t>
   </si>
   <si>
     <t>Hoja interactiva para calcular ahorro del doctor</t>
   </si>
   <si>
-    <t>7. Comisiones</t>
+    <t>6. Comisiones</t>
   </si>
   <si>
     <t>Cuánto ganas por cada venta (50% primer pago, 50% segundo)</t>
   </si>
   <si>
-    <t>8. Links y Demos</t>
+    <t>7. Links y Demos</t>
   </si>
   <si>
     <t>URLs importantes: demo, landing, WhatsApp soporte</t>
   </si>
   <si>
-    <t>9. Checklist de Venta</t>
+    <t>8. Checklist de Venta</t>
   </si>
   <si>
     <t>Pasos para cerrar un cliente</t>
@@ -125,40 +118,40 @@
     <t>BÁSICO</t>
   </si>
   <si>
+    <t>$149</t>
+  </si>
+  <si>
+    <t>$74 (50% off)</t>
+  </si>
+  <si>
+    <t>Doctores individuales. Comisión: $223.50 por venta.</t>
+  </si>
+  <si>
+    <t>PRO ⭐</t>
+  </si>
+  <si>
     <t>$299</t>
   </si>
   <si>
     <t>$149 (50% off)</t>
   </si>
   <si>
-    <t>Doctores individuales. Comisión: $448.50 por venta.</t>
-  </si>
-  <si>
-    <t>PRO ⭐</t>
-  </si>
-  <si>
-    <t>$599</t>
-  </si>
-  <si>
-    <t>$299 (50% off)</t>
-  </si>
-  <si>
     <t>Ilimitados</t>
   </si>
   <si>
-    <t>EL QUE MÁS VENDE. TODA la IA. Comisión: $898.50 por venta.</t>
+    <t>EL QUE MÁS VENDE. Odontograma + Portal + Multi-doctor. Comisión: $448.50 por venta.</t>
   </si>
   <si>
     <t>CLÍNICA</t>
   </si>
   <si>
-    <t>$1,199</t>
-  </si>
-  <si>
-    <t>$599 (50% off)</t>
-  </si>
-  <si>
-    <t>Clínicas grandes. Comisión: $1,798.50 por venta.</t>
+    <t>$499</t>
+  </si>
+  <si>
+    <t>$249 (50% off)</t>
+  </si>
+  <si>
+    <t>Clínicas grandes. Comisión: $748.50 por venta.</t>
   </si>
   <si>
     <t>✅ TODOS los planes de pago (Básico, Pro y Clínica) pagan comisión. Solo el plan Free NO.</t>
@@ -173,13 +166,13 @@
     <t>Free</t>
   </si>
   <si>
-    <t>Básico $299</t>
-  </si>
-  <si>
-    <t>Pro $599</t>
-  </si>
-  <si>
-    <t>Clínica $1,199</t>
+    <t>Básico $149</t>
+  </si>
+  <si>
+    <t>Pro $299</t>
+  </si>
+  <si>
+    <t>Clínica $499</t>
   </si>
   <si>
     <t>👥 Pacientes</t>
@@ -203,6 +196,9 @@
     <t>✅</t>
   </si>
   <si>
+    <t>════ ESENCIALES ════</t>
+  </si>
+  <si>
     <t>📄 Recetas PDF profesionales</t>
   </si>
   <si>
@@ -215,55 +211,28 @@
     <t>📲 Check-in con QR</t>
   </si>
   <si>
-    <t>🎤 Dictado por voz</t>
+    <t>📋 Expediente clínico completo</t>
+  </si>
+  <si>
+    <t>════ PRO ════</t>
+  </si>
+  <si>
+    <t>🦷 Odontograma interactivo</t>
   </si>
   <si>
     <t>✍️ Firma digital</t>
   </si>
   <si>
-    <t>🦷 Odontograma</t>
-  </si>
-  <si>
-    <t>════ FEATURES CON IA ════</t>
-  </si>
-  <si>
-    <t>🤖 Dictado inteligente con IA</t>
-  </si>
-  <si>
-    <t>🧠 Resumen IA del paciente</t>
-  </si>
-  <si>
-    <t>💡 Sugerencias de diagnóstico IA</t>
-  </si>
-  <si>
-    <t>📋 Consentimientos con IA</t>
-  </si>
-  <si>
-    <t>📊 Análisis IA del consultorio</t>
-  </si>
-  <si>
-    <t>🔮 Métricas predictivas</t>
-  </si>
-  <si>
-    <t>💬 Chatbot IA flotante</t>
-  </si>
-  <si>
-    <t>🎙️ Modo consulta en vivo</t>
-  </si>
-  <si>
-    <t>⌨️ Command Palette (Ctrl+K)</t>
-  </si>
-  <si>
-    <t>🗓️ Slot mágico en calendario</t>
-  </si>
-  <si>
-    <t>💬 Autoresponder WhatsApp IA</t>
-  </si>
-  <si>
-    <t>📝 Generador mensajes por paciente</t>
-  </si>
-  <si>
-    <t>════ PREMIUM ════</t>
+    <t>📋 Consentimientos digitales</t>
+  </si>
+  <si>
+    <t>👥 Portal del paciente</t>
+  </si>
+  <si>
+    <t>📊 Reportes avanzados</t>
+  </si>
+  <si>
+    <t>════ CLÍNICA ════</t>
   </si>
   <si>
     <t>📈 Reportes por doctor</t>
@@ -278,163 +247,16 @@
     <t>🎯 Onboarding 1 a 1</t>
   </si>
   <si>
-    <t>🤖 FEATURES CON INTELIGENCIA ARTIFICIAL</t>
-  </si>
-  <si>
-    <t>Qué hace</t>
-  </si>
-  <si>
-    <t>Ahorro al doctor</t>
-  </si>
-  <si>
-    <t>Pitch killer</t>
-  </si>
-  <si>
-    <t>Dictado inteligente</t>
-  </si>
-  <si>
-    <t>Habla toda la consulta y la IA llena diagnóstico, tratamiento, receta y notas automáticamente.</t>
-  </si>
-  <si>
-    <t>5 min/paciente</t>
-  </si>
-  <si>
-    <t>"Doctor, deja de teclear. Habla y yo escribo."</t>
-  </si>
-  <si>
-    <t>Resumen IA paciente</t>
-  </si>
-  <si>
-    <t>Al abrir un paciente, la IA te da un resumen narrativo en 2 segundos.</t>
-  </si>
-  <si>
-    <t>30 seg/paciente</t>
-  </si>
-  <si>
-    <t>"Entiende al paciente en 2 segundos sin leer 5 pantallas."</t>
-  </si>
-  <si>
-    <t>Sugerencias Dx</t>
-  </si>
-  <si>
-    <t>Escribes el motivo y la IA sugiere 3 diagnósticos con tratamiento y medicamento.</t>
-  </si>
-  <si>
-    <t>Consultas difíciles</t>
-  </si>
-  <si>
-    <t>"Es como tener un residente experto al lado."</t>
-  </si>
-  <si>
-    <t>Consentimientos IA</t>
-  </si>
-  <si>
-    <t>Escribes el procedimiento y la IA genera el consentimiento completo en 5 segundos.</t>
-  </si>
-  <si>
-    <t>20 min/consentimiento</t>
-  </si>
-  <si>
-    <t>"De 20 minutos a 5 segundos."</t>
-  </si>
-  <si>
-    <t>Análisis consultorio</t>
-  </si>
-  <si>
-    <t>La IA analiza tus datos y sugiere acciones: qué pacientes recuperar, cuándo subir precios, etc.</t>
-  </si>
-  <si>
-    <t>"Como tener un consultor de negocio 24/7."</t>
-  </si>
-  <si>
-    <t>Métricas predictivas</t>
-  </si>
-  <si>
-    <t>Predice ingresos, detecta pacientes que se van, sugiere precios óptimos.</t>
-  </si>
-  <si>
-    <t>"DocFácil te dice qué va a pasar en 2 semanas."</t>
-  </si>
-  <si>
-    <t>Chatbot IA flotante</t>
-  </si>
-  <si>
-    <t>Pregunta lo que sea: "cuánto facturé", "quién tiene cita mañana". Responde con datos reales.</t>
-  </si>
-  <si>
-    <t>20 clicks/día</t>
-  </si>
-  <si>
-    <t>"En lugar de navegar menús, le preguntas."</t>
-  </si>
-  <si>
-    <t>Modo consulta en vivo</t>
-  </si>
-  <si>
-    <t>La IA escucha toda la consulta (doctor+paciente) y llena el expediente al final.</t>
-  </si>
-  <si>
-    <t>"Tú atiendes, la IA escribe."</t>
-  </si>
-  <si>
-    <t>Command Palette</t>
-  </si>
-  <si>
-    <t>Ctrl+K en cualquier pantalla. Escribe lo que quieres hacer y aparece.</t>
-  </si>
-  <si>
-    <t>50 clicks/día</t>
-  </si>
-  <si>
-    <t>"Como Linear o Notion, pero para tu consultorio."</t>
-  </si>
-  <si>
-    <t>Slot mágico calendario</t>
-  </si>
-  <si>
-    <t>Dile "busca 30min mañana" y la IA te da los mejores horarios.</t>
-  </si>
-  <si>
-    <t>Reagendado más rápido</t>
-  </si>
-  <si>
-    <t>"Nunca más tetris mental con la agenda."</t>
-  </si>
-  <si>
-    <t>Autoresponder WhatsApp</t>
-  </si>
-  <si>
-    <t>Pacientes te escriben y la IA responde en tu nombre sobre citas, recetas, etc.</t>
-  </si>
-  <si>
-    <t>Recepcionista virtual</t>
-  </si>
-  <si>
-    <t>"Tu clínica contesta WhatsApp 24/7 sin contratar a nadie."</t>
-  </si>
-  <si>
-    <t>Generador mensajes</t>
-  </si>
-  <si>
-    <t>Botón para generar mensaje perfecto para cada paciente: recordatorio, seguimiento, cumpleaños, etc.</t>
-  </si>
-  <si>
-    <t>10 min/mensaje</t>
-  </si>
-  <si>
-    <t>"Retén pacientes sin escribir tú."</t>
-  </si>
-  <si>
     <t>⚔️ DOCFÁCIL vs COMPETENCIA</t>
   </si>
   <si>
     <t>Software</t>
   </si>
   <si>
-    <t>IA</t>
-  </si>
-  <si>
-    <t>Dictado</t>
+    <t>Odontograma</t>
+  </si>
+  <si>
+    <t>Firma digital</t>
   </si>
   <si>
     <t>WhatsApp</t>
@@ -449,9 +271,6 @@
     <t>DocFácil PRO ⭐</t>
   </si>
   <si>
-    <t>✅✅✅ 12 features</t>
-  </si>
-  <si>
     <t>✅ Automático</t>
   </si>
   <si>
@@ -488,7 +307,7 @@
     <t>❌ Local</t>
   </si>
   <si>
-    <t>💡 KEY INSIGHT: Eres el MÁS BARATO Y tienes las ÚNICAS features con IA del mercado mexicano.</t>
+    <t>💡 KEY INSIGHT: Eres el MÁS BARATO con odontograma, firma digital y WhatsApp automático del mercado mexicano.</t>
   </si>
   <si>
     <t>📞 SCRIPT DE VENTA + OBJECIONES</t>
@@ -500,7 +319,7 @@
     <t>Saludo inicial</t>
   </si>
   <si>
-    <t>"Hola Dr./Dra. [Nombre], soy [Tu nombre] de DocFácil. Te contacto porque somos el único software médico en México con Inteligencia Artificial integrada. ¿Tienes 3 minutos para ver cómo le ahorramos 2 horas al día a doctores como tú?"</t>
+    <t>"Hola Dr./Dra. [Nombre], soy [Tu nombre] de DocFácil. Te contacto porque ayudamos a doctores como tú a organizar su consultorio, recordar citas por WhatsApp automático y ahorrar 2 horas al día. ¿Tienes 3 minutos?"</t>
   </si>
   <si>
     <t>DOLOR</t>
@@ -509,7 +328,7 @@
     <t>Pregunta clave</t>
   </si>
   <si>
-    <t>"Doctor, ¿cuánto tiempo al día pasas tecleando expedientes en vez de atender pacientes?"</t>
+    <t>"Doctor, ¿cuánto tiempo al día pasas organizando citas en libreta o Excel?"</t>
   </si>
   <si>
     <t>Pregunta 2</t>
@@ -530,25 +349,31 @@
     <t>Punto 1</t>
   </si>
   <si>
-    <t>Muestra DICTADO INTELIGENTE: "Mira, oprimo grabar, hablo normal y la IA me llena todo: diagnóstico, tratamiento, receta."</t>
+    <t>Muestra AGENDA: "Aquí ves tu agenda del mes, arrastras citas para reagendar, bloqueas horarios con un clic."</t>
   </si>
   <si>
     <t>Punto 2</t>
   </si>
   <si>
-    <t>Muestra CHATBOT IA: "Ctrl+K, le pregunto cuánto facturé este mes y me responde con datos reales."</t>
+    <t>Muestra RECORDATORIOS: "Cada cita genera recordatorio automático 24h y 2h antes por WhatsApp."</t>
   </si>
   <si>
     <t>Punto 3</t>
   </si>
   <si>
-    <t>Muestra RECORDATORIOS: "Cada cita genera recordatorio automático 24h y 2h antes por WhatsApp."</t>
+    <t>Muestra RECETAS PDF: "Al terminar la consulta, un clic y se genera receta con tu cédula, membrete y firma."</t>
   </si>
   <si>
     <t>Punto 4</t>
   </si>
   <si>
-    <t>Muestra COBRO WhatsApp: "Al terminar la consulta, un click y el paciente recibe el cobro."</t>
+    <t>Muestra COBRO WhatsApp: "Al terminar la consulta, un clic y el paciente recibe el cobro."</t>
+  </si>
+  <si>
+    <t>Punto 5</t>
+  </si>
+  <si>
+    <t>Muestra ODONTOGRAMA/EXPEDIENTE: "Todo el historial clínico del paciente en una pantalla, con alertas de alergias y antecedentes."</t>
   </si>
   <si>
     <t>CIERRE</t>
@@ -557,7 +382,7 @@
     <t>Frase de cierre</t>
   </si>
   <si>
-    <t>"Doctor, por $599 al mes estás ganando 2 horas al día = $10,000 extra al mes. DocFácil se paga 16 veces."</t>
+    <t>"Doctor, por $299 al mes ahorras 2 horas al día y recuperas 8 pacientes que antes no llegaban = $4,800 extra al mes. DocFácil se paga 16 veces."</t>
   </si>
   <si>
     <t>Call to action</t>
@@ -572,19 +397,19 @@
     <t>"Es caro"</t>
   </si>
   <si>
-    <t>"Doctor, ¿cuánto cobras por consulta? ¿$500? DocFácil Pro cuesta MENOS de 1 consulta y te ahorra 40 pacientes al mes en tiempo. Se paga 40 veces."</t>
+    <t>"Doctor, ¿cuánto cobras por consulta? ¿$500? DocFácil Pro cuesta MENOS de 1 consulta al mes y te ahorra 8 pacientes en recordatorios WhatsApp. Se paga 16 veces."</t>
   </si>
   <si>
     <t>"No soy tecnológico"</t>
   </si>
   <si>
-    <t>"Por eso la IA. No tienes que aprender nada. Literalmente hablas y la app escribe. Si sabes usar WhatsApp, sabes usar DocFácil."</t>
+    <t>"Por eso lo diseñamos simple. Si sabes usar WhatsApp, sabes usar DocFácil. Te acompañamos en la configuración inicial sin costo."</t>
   </si>
   <si>
     <t>"Ya tengo software"</t>
   </si>
   <si>
-    <t>"¿Tiene IA que escribe expedientes? ¿Tiene chatbot que responde preguntas? ¿Predice tus ingresos? Somos los únicos. Pruébalo 14 días gratis sin cancelar lo actual."</t>
+    <t>"¿Es en la nube o instalado en una sola compu? ¿Manda recordatorios WhatsApp automáticos? ¿Tiene portal del paciente? Pruébalo 14 días gratis sin cancelar lo actual."</t>
   </si>
   <si>
     <t>"Mis datos están seguros?"</t>
@@ -644,12 +469,6 @@
     <t>Citas que se salvan x precio</t>
   </si>
   <si>
-    <t>Extra por dictado IA (atiendes más pacientes)</t>
-  </si>
-  <si>
-    <t>1 paciente extra al día x precio</t>
-  </si>
-  <si>
     <t>TOTAL AHORRO/MES</t>
   </si>
   <si>
@@ -665,7 +484,7 @@
     <t>💰 ESQUEMA DE COMISIONES</t>
   </si>
   <si>
-    <t>🎯 GANAS 1.5 MENSUALIDADES POR CADA CLIENTE PRO o CLÍNICA</t>
+    <t>🎯 GANAS 1.5 MENSUALIDADES POR CADA CLIENTE DE PAGO (Básico, Pro o Clínica)</t>
   </si>
   <si>
     <t>Se paga 50% con el primer pago del cliente, 50% con el segundo pago</t>
@@ -686,28 +505,28 @@
     <t>Básico</t>
   </si>
   <si>
+    <t>$223.50</t>
+  </si>
+  <si>
+    <t>$111.75 + $111.75</t>
+  </si>
+  <si>
+    <t>Pro ⭐</t>
+  </si>
+  <si>
     <t>$448.50</t>
   </si>
   <si>
     <t>$224.25 + $224.25</t>
   </si>
   <si>
-    <t>Pro ⭐</t>
-  </si>
-  <si>
-    <t>$898.50</t>
-  </si>
-  <si>
-    <t>$449.25 + $449.25</t>
-  </si>
-  <si>
     <t>Clínica</t>
   </si>
   <si>
-    <t>$1,798.50</t>
-  </si>
-  <si>
-    <t>$899.25 + $899.25</t>
+    <t>$748.50</t>
+  </si>
+  <si>
+    <t>$374.25 + $374.25</t>
   </si>
   <si>
     <t>📊 METAS MENSUALES PARA VENDEDOR</t>
@@ -731,10 +550,10 @@
     <t>3 Básico + 2 Pro</t>
   </si>
   <si>
-    <t>3x$448.50 + 2x$898.50</t>
-  </si>
-  <si>
-    <t>$3,142.50</t>
+    <t>3x$223.50 + 2x$448.50</t>
+  </si>
+  <si>
+    <t>$1,567.50</t>
   </si>
   <si>
     <t>Medium</t>
@@ -743,10 +562,10 @@
     <t>5 Pro + 1 Clínica</t>
   </si>
   <si>
-    <t>5x$898.50 + 1x$1,798.50</t>
-  </si>
-  <si>
-    <t>$6,291</t>
+    <t>5x$448.50 + 1x$748.50</t>
+  </si>
+  <si>
+    <t>$2,991</t>
   </si>
   <si>
     <t>Top</t>
@@ -755,10 +574,10 @@
     <t>10 Pro + 2 Clínica</t>
   </si>
   <si>
-    <t>10x$898.50 + 2x$1,798.50</t>
-  </si>
-  <si>
-    <t>$12,582</t>
+    <t>10x$448.50 + 2x$748.50</t>
+  </si>
+  <si>
+    <t>$5,982</t>
   </si>
   <si>
     <t>Elite</t>
@@ -770,7 +589,7 @@
     <t>Mix completo</t>
   </si>
   <si>
-    <t>$16,618.50</t>
+    <t>$7,843.50</t>
   </si>
   <si>
     <t>🔗 LINKS IMPORTANTES</t>
@@ -857,13 +676,13 @@
     <t>Demo en vivo</t>
   </si>
   <si>
-    <t>Mostrar dictado IA + chatbot IA + recordatorios</t>
+    <t>Mostrar agenda + recordatorios WhatsApp + recetas PDF + cobro por WhatsApp</t>
   </si>
   <si>
     <t>Cotización</t>
   </si>
   <si>
-    <t>Mostrar Plan Pro $599 con 50% descuento = $299 de por vida (fundador)</t>
+    <t>Mostrar Plan Pro $299 con 50% descuento = $149 de por vida (fundador)</t>
   </si>
   <si>
     <t>Objeciones</t>
@@ -922,7 +741,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -1011,15 +830,6 @@
       <u val="none"/>
       <sz val="11"/>
       <color rgb="FF7C3AED"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="1"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FF0D9488"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1187,7 +997,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="38">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -1216,51 +1026,42 @@
     <xf xfId="0" fontId="9" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="9" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="7" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="10" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="12" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="11" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="13" numFmtId="0" fillId="8" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="8" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="9" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="9" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="14" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="13" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="14" numFmtId="164" fillId="4" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="15" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="15" numFmtId="165" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="13" numFmtId="164" fillId="4" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="14" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="14" numFmtId="165" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="5" numFmtId="0" fillId="8" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="16" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="15" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="17" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="16" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
@@ -1270,8 +1071,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="18" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
-    <xf xfId="0" fontId="19" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="17" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="18" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
@@ -1574,7 +1375,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="true" style="0"/>
@@ -1665,14 +1466,6 @@
       </c>
       <c r="B13" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1689,189 +1482,6 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-  </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="true" style="0"/>
-    <col min="2" max="2" width="30" customWidth="true" style="0"/>
-    <col min="3" max="3" width="60" customWidth="true" style="0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" customHeight="1" ht="40">
-      <c r="A1" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" customHeight="1" ht="25">
-      <c r="A3" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B3" s="40" t="s">
-        <v>268</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" customHeight="1" ht="25">
-      <c r="A4" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>270</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" customHeight="1" ht="25">
-      <c r="A5" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>272</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" customHeight="1" ht="25">
-      <c r="A6" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" customHeight="1" ht="25">
-      <c r="A7" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>276</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" customHeight="1" ht="25">
-      <c r="A8" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>278</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" customHeight="1" ht="25">
-      <c r="A9" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" customHeight="1" ht="25">
-      <c r="A10" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>282</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" customHeight="1" ht="25">
-      <c r="A11" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B11" s="40" t="s">
-        <v>284</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" customHeight="1" ht="25">
-      <c r="A12" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" customHeight="1" ht="25">
-      <c r="A13" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>288</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" customHeight="1" ht="25">
-      <c r="A14" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B14" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" customHeight="1" ht="25">
-      <c r="A15" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B15" s="40" t="s">
-        <v>292</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" customHeight="1" ht="25">
-      <c r="A16" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="B16" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>295</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells>
-    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1897,38 +1507,38 @@
   <sheetData>
     <row r="1" spans="1:6" customHeight="1" ht="40">
       <c r="A1" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:6" customHeight="1" ht="25">
       <c r="A3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>30</v>
       </c>
       <c r="D4" s="8">
         <v>1</v>
@@ -1937,18 +1547,18 @@
         <v>30</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="D5" s="8">
         <v>1</v>
@@ -1957,52 +1567,52 @@
         <v>200</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>38</v>
       </c>
       <c r="D6" s="9">
         <v>3</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:6" customHeight="1" ht="25">
       <c r="A10" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2021,7 +1631,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="true" style="0"/>
@@ -2033,29 +1643,29 @@
   <sheetData>
     <row r="1" spans="1:5" customHeight="1" ht="40">
       <c r="A1" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5" customHeight="1" ht="25">
       <c r="A3" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B4" s="12">
         <v>30</v>
@@ -2064,32 +1674,32 @@
         <v>200</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B5" s="12">
         <v>20</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B6" s="12">
         <v>1</v>
@@ -2101,143 +1711,121 @@
         <v>3</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="8"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="13" t="s">
         <v>57</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2249,298 +1837,180 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>58</v>
-      </c>
+      <c r="A22" s="8"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>58</v>
+      <c r="A23" s="13" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="8"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A9:E9"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A23:E23"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2549,217 +2019,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="25" customWidth="true" style="0"/>
-    <col min="2" max="2" width="50" customWidth="true" style="0"/>
-    <col min="3" max="3" width="25" customWidth="true" style="0"/>
-    <col min="4" max="4" width="50" customWidth="true" style="0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" customHeight="1" ht="40">
-      <c r="A1" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" customHeight="1" ht="25">
-      <c r="A3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" customHeight="1" ht="50">
-      <c r="A4" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" customHeight="1" ht="50">
-      <c r="A5" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" customHeight="1" ht="50">
-      <c r="A6" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" customHeight="1" ht="50">
-      <c r="A7" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" customHeight="1" ht="50">
-      <c r="A8" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" customHeight="1" ht="50">
-      <c r="A9" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" customHeight="1" ht="50">
-      <c r="A10" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" customHeight="1" ht="50">
-      <c r="A11" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" customHeight="1" ht="50">
-      <c r="A12" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" customHeight="1" ht="50">
-      <c r="A13" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" customHeight="1" ht="50">
-      <c r="A14" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" customHeight="1" ht="50">
-      <c r="A15" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>132</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells>
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2777,157 +2036,366 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" customHeight="1" ht="40">
-      <c r="A1" s="18" t="s">
-        <v>133</v>
+      <c r="A1" s="14" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="11" t="s">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>139</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>58</v>
+        <v>81</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="8" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="8" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="8" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="8" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:7" customHeight="1" ht="30">
-      <c r="A11" s="21" t="s">
-        <v>154</v>
+      <c r="A11" s="17" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A11:G11"/>
+  </mergeCells>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="true" style="0"/>
+    <col min="2" max="2" width="90" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" customHeight="1" ht="40">
+      <c r="A1" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" customHeight="1" ht="50">
+      <c r="A4" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" customHeight="1" ht="50">
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" customHeight="1" ht="50">
+      <c r="A7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" customHeight="1" ht="50">
+      <c r="A8" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" customHeight="1" ht="50">
+      <c r="A9" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" customHeight="1" ht="50">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" customHeight="1" ht="50">
+      <c r="A12" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" customHeight="1" ht="50">
+      <c r="A13" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" customHeight="1" ht="50">
+      <c r="A14" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" customHeight="1" ht="50">
+      <c r="A15" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" customHeight="1" ht="50">
+      <c r="A16" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" customHeight="1" ht="50">
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" customHeight="1" ht="50">
+      <c r="A19" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" customHeight="1" ht="50">
+      <c r="A20" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" customHeight="1" ht="50">
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" customHeight="1" ht="50">
+      <c r="A23" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" customHeight="1" ht="50">
+      <c r="A24" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" customHeight="1" ht="50">
+      <c r="A25" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" customHeight="1" ht="50">
+      <c r="A26" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" customHeight="1" ht="50">
+      <c r="A27" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" customHeight="1" ht="50">
+      <c r="A28" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2940,208 +2408,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="25" customWidth="true" style="0"/>
-    <col min="2" max="2" width="90" customWidth="true" style="0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" customHeight="1" ht="40">
-      <c r="A1" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="22" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" customHeight="1" ht="50">
-      <c r="A4" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" customHeight="1" ht="50">
-      <c r="A5" s="23"/>
-      <c r="B5" s="16"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="22" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" customHeight="1" ht="50">
-      <c r="A7" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" customHeight="1" ht="50">
-      <c r="A8" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" customHeight="1" ht="50">
-      <c r="A9" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" customHeight="1" ht="50">
-      <c r="A10" s="23"/>
-      <c r="B10" s="16"/>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="22" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" customHeight="1" ht="50">
-      <c r="A12" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" customHeight="1" ht="50">
-      <c r="A13" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" customHeight="1" ht="50">
-      <c r="A14" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" customHeight="1" ht="50">
-      <c r="A15" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" customHeight="1" ht="50">
-      <c r="A16" s="23"/>
-      <c r="B16" s="16"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="22" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" customHeight="1" ht="50">
-      <c r="A18" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" customHeight="1" ht="50">
-      <c r="A19" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" customHeight="1" ht="50">
-      <c r="A20" s="23"/>
-      <c r="B20" s="16"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="22" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" customHeight="1" ht="50">
-      <c r="A22" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" customHeight="1" ht="50">
-      <c r="A23" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" customHeight="1" ht="50">
-      <c r="A24" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" customHeight="1" ht="50">
-      <c r="A25" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" customHeight="1" ht="50">
-      <c r="A26" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" customHeight="1" ht="50">
-      <c r="A27" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>192</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A21:B21"/>
-  </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="true" style="0"/>
@@ -3150,116 +2417,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" customHeight="1" ht="40">
-      <c r="A1" s="24" t="s">
-        <v>193</v>
+      <c r="A1" s="21" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4" s="25">
+        <v>137</v>
+      </c>
+      <c r="B4" s="22">
         <v>80</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>196</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="25">
+        <v>139</v>
+      </c>
+      <c r="B5" s="22">
         <v>500</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>198</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B6" s="25">
+        <v>141</v>
+      </c>
+      <c r="B6" s="22">
         <v>10</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>200</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="20" t="s">
-        <v>201</v>
+      <c r="A8" s="16" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B9" s="28">
+        <v>144</v>
+      </c>
+      <c r="B9" s="25">
         <f>B6*0.6*4*(B5/0.5)</f>
         <v>24000</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="28">
+        <v>146</v>
+      </c>
+      <c r="B10" s="25">
         <f>B4*0.08*B5</f>
         <v>3200</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>205</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="28">
-        <f>20*B5*0.15</f>
-        <v>1500</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="B12" s="29">
-        <f>B9+B10+B11</f>
-        <v>28700</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>209</v>
+      <c r="A11" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="26">
+        <f>B9+B10</f>
+        <v>27200</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="23">
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>210</v>
-      </c>
-      <c r="B14" s="26">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="B15" s="31">
-        <f>B12/B14</f>
-        <v>47.91318864774625</v>
+      <c r="A14" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="28">
+        <f>B11/B13</f>
+        <v>90.96989966555184</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +2529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3289,163 +2544,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" customHeight="1" ht="40">
-      <c r="A1" s="32" t="s">
-        <v>212</v>
+      <c r="A1" s="29" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="33" t="s">
-        <v>213</v>
+      <c r="A3" s="30" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="34" t="s">
-        <v>214</v>
+      <c r="A4" s="31" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:4" customHeight="1" ht="25">
       <c r="A6" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>217</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>219</v>
+        <v>159</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>221</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>224</v>
+      <c r="A9" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>227</v>
+      <c r="A10" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="35" t="s">
-        <v>228</v>
+      <c r="A13" s="32" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>232</v>
+      <c r="A15" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>233</v>
+        <v>173</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>234</v>
+        <v>174</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>235</v>
+        <v>175</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>236</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>237</v>
+        <v>177</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>241</v>
+        <v>181</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>243</v>
+        <v>183</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="12" t="s">
-        <v>245</v>
+        <v>185</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>246</v>
+        <v>186</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>248</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -3461,7 +2716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3475,71 +2730,71 @@
   <sheetData>
     <row r="1" spans="1:2" customHeight="1" ht="40">
       <c r="A1" s="5" t="s">
-        <v>249</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:2" customHeight="1" ht="25">
-      <c r="A3" s="37" t="s">
-        <v>250</v>
-      </c>
-      <c r="B3" s="38" t="s">
-        <v>251</v>
+      <c r="A3" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:2" customHeight="1" ht="25">
-      <c r="A4" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>253</v>
+      <c r="A4" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:2" customHeight="1" ht="25">
-      <c r="A5" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>255</v>
+      <c r="A5" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:2" customHeight="1" ht="25">
-      <c r="A6" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>257</v>
+      <c r="A6" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:2" customHeight="1" ht="25">
-      <c r="A7" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>259</v>
+      <c r="A7" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:2" customHeight="1" ht="25">
-      <c r="A8" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>261</v>
+      <c r="A8" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:2" customHeight="1" ht="25">
-      <c r="A9" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>263</v>
+      <c r="A9" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:2" customHeight="1" ht="25">
-      <c r="A10" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>265</v>
+      <c r="A10" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3550,4 +2805,186 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="true" style="0"/>
+    <col min="2" max="2" width="30" customWidth="true" style="0"/>
+    <col min="3" max="3" width="60" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" customHeight="1" ht="40">
+      <c r="A1" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" customHeight="1" ht="25">
+      <c r="A3" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" customHeight="1" ht="25">
+      <c r="A4" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" customHeight="1" ht="25">
+      <c r="A5" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" customHeight="1" ht="25">
+      <c r="A6" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" customHeight="1" ht="25">
+      <c r="A7" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" customHeight="1" ht="25">
+      <c r="A8" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" customHeight="1" ht="25">
+      <c r="A9" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" customHeight="1" ht="25">
+      <c r="A10" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" customHeight="1" ht="25">
+      <c r="A11" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" customHeight="1" ht="25">
+      <c r="A12" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" customHeight="1" ht="25">
+      <c r="A13" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" customHeight="1" ht="25">
+      <c r="A14" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" customHeight="1" ht="25">
+      <c r="A15" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" customHeight="1" ht="25">
+      <c r="A16" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
 </file>
--- a/docs/DocFacil-Kit-Vendedor-2026.xlsx
+++ b/docs/DocFacil-Kit-Vendedor-2026.xlsx
@@ -124,7 +124,7 @@
     <t>$74 (50% off)</t>
   </si>
   <si>
-    <t>Doctores individuales. Comisión: $223.50 por venta.</t>
+    <t>Doctores individuales. Comisión: $447 por venta.</t>
   </si>
   <si>
     <t>PRO ⭐</t>
@@ -139,7 +139,7 @@
     <t>Ilimitados</t>
   </si>
   <si>
-    <t>EL QUE MÁS VENDE. Odontograma + Portal + Multi-doctor. Comisión: $448.50 por venta.</t>
+    <t>EL QUE MÁS VENDE. Odontograma + Portal + Multi-doctor. Comisión: $897 por venta.</t>
   </si>
   <si>
     <t>CLÍNICA</t>
@@ -151,7 +151,7 @@
     <t>$249 (50% off)</t>
   </si>
   <si>
-    <t>Clínicas grandes. Comisión: $748.50 por venta.</t>
+    <t>Clínicas grandes. Comisión: $1,497 por venta.</t>
   </si>
   <si>
     <t>✅ TODOS los planes de pago (Básico, Pro y Clínica) pagan comisión. Solo el plan Free NO.</t>
@@ -484,7 +484,7 @@
     <t>💰 ESQUEMA DE COMISIONES</t>
   </si>
   <si>
-    <t>🎯 GANAS 1.5 MENSUALIDADES POR CADA CLIENTE DE PAGO (Básico, Pro o Clínica)</t>
+    <t>🎯 GANAS 3 MENSUALIDADES POR CADA CLIENTE DE PAGO (Básico, Pro o Clínica)</t>
   </si>
   <si>
     <t>Se paga 50% con el primer pago del cliente, 50% con el segundo pago</t>
@@ -493,7 +493,7 @@
     <t>Precio cliente/mes</t>
   </si>
   <si>
-    <t>Comisión total (1.5x)</t>
+    <t>Comisión total (3x)</t>
   </si>
   <si>
     <t>½ primer pago + ½ segundo pago</t>
@@ -505,28 +505,28 @@
     <t>Básico</t>
   </si>
   <si>
-    <t>$223.50</t>
-  </si>
-  <si>
-    <t>$111.75 + $111.75</t>
+    <t>$447</t>
+  </si>
+  <si>
+    <t>$223.50 + $223.50</t>
   </si>
   <si>
     <t>Pro ⭐</t>
   </si>
   <si>
-    <t>$448.50</t>
-  </si>
-  <si>
-    <t>$224.25 + $224.25</t>
+    <t>$897</t>
+  </si>
+  <si>
+    <t>$448.50 + $448.50</t>
   </si>
   <si>
     <t>Clínica</t>
   </si>
   <si>
-    <t>$748.50</t>
-  </si>
-  <si>
-    <t>$374.25 + $374.25</t>
+    <t>$1,497</t>
+  </si>
+  <si>
+    <t>$748.50 + $748.50</t>
   </si>
   <si>
     <t>📊 METAS MENSUALES PARA VENDEDOR</t>
@@ -550,10 +550,10 @@
     <t>3 Básico + 2 Pro</t>
   </si>
   <si>
-    <t>3x$223.50 + 2x$448.50</t>
-  </si>
-  <si>
-    <t>$1,567.50</t>
+    <t>3x$447 + 2x$897</t>
+  </si>
+  <si>
+    <t>$3,135</t>
   </si>
   <si>
     <t>Medium</t>
@@ -562,10 +562,10 @@
     <t>5 Pro + 1 Clínica</t>
   </si>
   <si>
-    <t>5x$448.50 + 1x$748.50</t>
-  </si>
-  <si>
-    <t>$2,991</t>
+    <t>5x$897 + 1x$1,497</t>
+  </si>
+  <si>
+    <t>$5,982</t>
   </si>
   <si>
     <t>Top</t>
@@ -574,10 +574,10 @@
     <t>10 Pro + 2 Clínica</t>
   </si>
   <si>
-    <t>10x$448.50 + 2x$748.50</t>
-  </si>
-  <si>
-    <t>$5,982</t>
+    <t>10x$897 + 2x$1,497</t>
+  </si>
+  <si>
+    <t>$11,964</t>
   </si>
   <si>
     <t>Elite</t>
